--- a/data/trans_dic/P32-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P32-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que piensa que debería beber menos</t>
+          <t>Población que piensa que debería beber menos (tasa de respuesta: 99,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,66</t>
+          <t>0,39; 2,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,48; 9,48</t>
+          <t>4,45; 9,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,9; 5,49</t>
+          <t>1,9; 5,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,16; 4,34</t>
+          <t>1,1; 4,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,43</t>
+          <t>0,53; 4,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,72</t>
+          <t>0,91; 5,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,1</t>
+          <t>0,42; 3,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,8</t>
+          <t>0,17; 1,91</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,56; 7,23</t>
+          <t>3,58; 7,17</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,95; 5,09</t>
+          <t>1,93; 4,74</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,53</t>
+          <t>1,14; 3,3</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,65; 4,39</t>
+          <t>1,67; 4,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,26; 7,38</t>
+          <t>3,34; 7,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,78; 7,91</t>
+          <t>3,69; 7,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,64; 8,91</t>
+          <t>3,78; 8,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,86</t>
+          <t>0,0; 2,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 4,23</t>
+          <t>0,53; 4,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,15; 4,5</t>
+          <t>1,17; 4,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,62; 9,0</t>
+          <t>2,67; 9,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,25</t>
+          <t>1,34; 3,46</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,59; 5,67</t>
+          <t>2,59; 5,56</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,08; 5,91</t>
+          <t>3,17; 6,1</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,99; 8,01</t>
+          <t>3,66; 7,8</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,43; 7,06</t>
+          <t>2,44; 7,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,86; 11,52</t>
+          <t>5,93; 11,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,91; 7,34</t>
+          <t>2,87; 7,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,9; 9,91</t>
+          <t>3,79; 10,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,24</t>
+          <t>0,0; 4,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,8</t>
+          <t>0,48; 4,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 4,86</t>
+          <t>0,88; 4,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 6,23</t>
+          <t>0,26; 6,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,07; 5,39</t>
+          <t>2,16; 5,71</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,72; 8,91</t>
+          <t>4,45; 8,48</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,64; 5,91</t>
+          <t>2,45; 5,65</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,48; 6,77</t>
+          <t>1,62; 6,75</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,79; 5,04</t>
+          <t>1,8; 4,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,43; 10,22</t>
+          <t>5,45; 10,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,49; 8,75</t>
+          <t>4,68; 9,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,8; 13,06</t>
+          <t>6,78; 13,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,45; 5,91</t>
+          <t>1,43; 5,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,34; 5,18</t>
+          <t>1,37; 5,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,77; 7,37</t>
+          <t>2,86; 7,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,44</t>
+          <t>0,51; 2,58</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,96; 4,37</t>
+          <t>1,98; 4,32</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,33; 7,56</t>
+          <t>4,08; 7,58</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,48; 7,65</t>
+          <t>4,61; 7,71</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,55; 8,54</t>
+          <t>4,57; 8,78</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,08; 3,7</t>
+          <t>2,07; 3,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,63; 7,92</t>
+          <t>5,66; 7,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,31; 6,45</t>
+          <t>4,28; 6,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,85; 7,64</t>
+          <t>4,94; 7,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,54</t>
+          <t>0,79; 2,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,34</t>
+          <t>1,32; 3,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,36; 4,51</t>
+          <t>2,32; 4,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,67</t>
+          <t>1,22; 3,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,81; 2,96</t>
+          <t>1,83; 3,0</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,42; 6,13</t>
+          <t>4,33; 6,06</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,78; 5,39</t>
+          <t>3,73; 5,27</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,58; 5,76</t>
+          <t>3,58; 5,78</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que piensa que debería beber menos</t>
+          <t>Población que piensa que debería beber menos (tasa de respuesta: 99,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1353; 11686</t>
+          <t>1701; 11413</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19134; 40522</t>
+          <t>19008; 39310</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8177; 23588</t>
+          <t>8173; 22818</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3854; 14486</t>
+          <t>3673; 13681</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 1883</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>928; 7776</t>
+          <t>924; 8726</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1639; 10462</t>
+          <t>1669; 10442</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>841; 6558</t>
+          <t>674; 6081</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1054; 11183</t>
+          <t>1064; 11813</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21452; 43546</t>
+          <t>21569; 43231</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11961; 31178</t>
+          <t>11846; 29027</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6028; 17406</t>
+          <t>5623; 16285</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9601; 25522</t>
+          <t>9733; 28532</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19287; 43728</t>
+          <t>19763; 42743</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21648; 45298</t>
+          <t>21115; 45349</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17348; 42474</t>
+          <t>18032; 42150</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 7998</t>
+          <t>0; 7919</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1075; 12553</t>
+          <t>1564; 12651</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3717; 14513</t>
+          <t>3773; 14499</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5264; 18076</t>
+          <t>5362; 18932</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11019; 28015</t>
+          <t>11584; 29805</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22981; 50363</t>
+          <t>23052; 49461</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27588; 52855</t>
+          <t>28333; 54553</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>27011; 54313</t>
+          <t>24790; 52837</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8051; 23363</t>
+          <t>8074; 23355</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>27012; 53060</t>
+          <t>27301; 51366</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12388; 31234</t>
+          <t>12238; 32046</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12692; 32250</t>
+          <t>12341; 33118</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6830</t>
+          <t>0; 6297</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>993; 9970</t>
+          <t>994; 8866</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2061; 11280</t>
+          <t>2048; 11410</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>771; 23419</t>
+          <t>963; 22719</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9560; 24867</t>
+          <t>9950; 26367</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>31559; 59514</t>
+          <t>29754; 56678</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17373; 38859</t>
+          <t>16108; 37164</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10388; 47462</t>
+          <t>11374; 47379</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9440; 26623</t>
+          <t>9489; 25496</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>30429; 57251</t>
+          <t>30517; 57761</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25723; 50095</t>
+          <t>26789; 51795</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>30162; 57954</t>
+          <t>30079; 59864</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4395; 17974</t>
+          <t>4353; 18057</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4982; 19227</t>
+          <t>5070; 21526</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11323; 30158</t>
+          <t>11717; 30000</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1447; 7060</t>
+          <t>1485; 7481</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16357; 36407</t>
+          <t>16516; 36010</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>40293; 70448</t>
+          <t>38034; 70596</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>43918; 75079</t>
+          <t>45265; 75703</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>33331; 62624</t>
+          <t>33540; 64393</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>39191; 69535</t>
+          <t>38924; 66093</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>114844; 161660</t>
+          <t>115514; 162242</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>86191; 129082</t>
+          <t>85564; 128607</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>76577; 120635</t>
+          <t>77979; 121734</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6959; 22689</t>
+          <t>7108; 22856</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14266; 35088</t>
+          <t>13863; 34593</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>27059; 51661</t>
+          <t>26546; 51518</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>12219; 37688</t>
+          <t>12493; 37468</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>50238; 82102</t>
+          <t>50788; 83364</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>136494; 189385</t>
+          <t>133873; 187440</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>118964; 169567</t>
+          <t>117227; 165883</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>93260; 150209</t>
+          <t>93197; 150627</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P32-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P32-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,6</t>
+          <t>0,21; 2,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,45; 9,2</t>
+          <t>4,54; 9,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,9; 5,31</t>
+          <t>1,91; 5,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,1; 4,1</t>
+          <t>1,1; 3,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,37 +742,37 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,97</t>
+          <t>0,53; 4,51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,91; 5,71</t>
+          <t>0,9; 5,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,8</t>
+          <t>0,5; 3,83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,91</t>
+          <t>0,28; 1,99</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,58; 7,17</t>
+          <t>3,52; 6,98</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,74</t>
+          <t>1,94; 4,68</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,3</t>
+          <t>1,05; 3,21</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,67; 4,9</t>
+          <t>1,71; 4,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,34; 7,22</t>
+          <t>3,39; 7,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,69; 7,92</t>
+          <t>3,59; 7,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,78; 8,84</t>
+          <t>3,73; 8,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,83</t>
+          <t>0,0; 2,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,27</t>
+          <t>0,36; 4,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,17; 4,5</t>
+          <t>1,16; 4,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,67; 9,42</t>
+          <t>2,73; 8,84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,46</t>
+          <t>1,29; 3,42</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,59; 5,56</t>
+          <t>2,64; 5,5</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,17; 6,1</t>
+          <t>3,05; 6,14</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,66; 7,8</t>
+          <t>4,06; 7,95</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,44; 7,06</t>
+          <t>2,39; 7,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,93; 11,15</t>
+          <t>6,01; 11,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,87; 7,53</t>
+          <t>2,97; 7,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,79; 10,18</t>
+          <t>4,96; 11,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,83</t>
+          <t>0,0; 5,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,27</t>
+          <t>0,47; 4,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 4,91</t>
+          <t>0,88; 5,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 6,04</t>
+          <t>2,6; 10,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,16; 5,71</t>
+          <t>2,12; 5,59</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,45; 8,48</t>
+          <t>4,61; 8,52</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,45; 5,65</t>
+          <t>2,54; 5,63</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,62; 6,75</t>
+          <t>4,75; 9,65</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,82</t>
+          <t>1,74; 4,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,45; 10,31</t>
+          <t>5,37; 9,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,68; 9,05</t>
+          <t>4,69; 8,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,78; 13,49</t>
+          <t>6,92; 13,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,43; 5,94</t>
+          <t>1,19; 5,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,37; 5,8</t>
+          <t>1,24; 5,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,86; 7,34</t>
+          <t>3,14; 7,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,58</t>
+          <t>0,75; 5,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,32</t>
+          <t>1,96; 4,54</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,08; 7,58</t>
+          <t>4,08; 7,42</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,61; 7,71</t>
+          <t>4,37; 7,52</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,57; 8,78</t>
+          <t>4,74; 8,86</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,07; 3,51</t>
+          <t>2,08; 3,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,66; 7,95</t>
+          <t>5,61; 8,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,28; 6,43</t>
+          <t>4,32; 6,38</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,94; 7,71</t>
+          <t>5,2; 8,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,55</t>
+          <t>0,8; 2,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,29</t>
+          <t>1,31; 3,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,32; 4,49</t>
+          <t>2,39; 4,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,65</t>
+          <t>2,4; 5,02</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,83; 3,0</t>
+          <t>1,8; 2,94</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,33; 6,06</t>
+          <t>4,4; 6,01</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,73; 5,27</t>
+          <t>3,84; 5,34</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,58; 5,78</t>
+          <t>4,59; 6,54</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7636</t>
+          <t>7718</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2581</t>
+          <t>2630</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10217</t>
+          <t>10348</t>
         </is>
       </c>
     </row>
@@ -1645,22 +1645,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1701; 11413</t>
+          <t>917; 11137</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19008; 39310</t>
+          <t>19414; 39826</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8173; 22818</t>
+          <t>8199; 23777</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3673; 13681</t>
+          <t>3889; 13673</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1670,37 +1670,37 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>924; 8726</t>
+          <t>934; 7919</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1669; 10442</t>
+          <t>1653; 9762</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>674; 6081</t>
+          <t>860; 6629</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1064; 11813</t>
+          <t>1733; 12337</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21569; 43231</t>
+          <t>21234; 42055</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11846; 29027</t>
+          <t>11892; 28648</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5623; 16285</t>
+          <t>5546; 16892</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27337</t>
+          <t>29296</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9966</t>
+          <t>11512</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>37303</t>
+          <t>40808</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9733; 28532</t>
+          <t>9958; 27982</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19763; 42743</t>
+          <t>20085; 42214</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21115; 45349</t>
+          <t>20569; 44821</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18032; 42150</t>
+          <t>18679; 44141</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 7919</t>
+          <t>0; 6765</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1564; 12651</t>
+          <t>1070; 12054</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3773; 14499</t>
+          <t>3735; 15043</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5362; 18932</t>
+          <t>6099; 19736</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11584; 29805</t>
+          <t>11145; 29453</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23052; 49461</t>
+          <t>23509; 48843</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28333; 54553</t>
+          <t>27253; 54937</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>24790; 52837</t>
+          <t>29396; 57567</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20523</t>
+          <t>27650</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8374</t>
+          <t>11232</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28897</t>
+          <t>38882</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8074; 23355</t>
+          <t>7922; 23513</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>27301; 51366</t>
+          <t>27699; 53695</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12238; 32046</t>
+          <t>12629; 32291</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12341; 33118</t>
+          <t>17871; 41994</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6297</t>
+          <t>0; 7275</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>994; 8866</t>
+          <t>984; 9195</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2048; 11410</t>
+          <t>2046; 12087</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>963; 22719</t>
+          <t>5237; 21033</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9950; 26367</t>
+          <t>9795; 25787</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>29754; 56678</t>
+          <t>30833; 56926</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16108; 37164</t>
+          <t>16689; 37035</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11374; 47379</t>
+          <t>26641; 54165</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>42240</t>
+          <t>44522</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3566</t>
+          <t>5873</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>45805</t>
+          <t>50395</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9489; 25496</t>
+          <t>9189; 25447</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>30517; 57761</t>
+          <t>30075; 55701</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26789; 51795</t>
+          <t>26821; 51115</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>30079; 59864</t>
+          <t>32214; 64083</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4353; 18057</t>
+          <t>3619; 16905</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5070; 21526</t>
+          <t>4611; 19503</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11717; 30000</t>
+          <t>12825; 30954</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1485; 7481</t>
+          <t>2307; 15499</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16516; 36010</t>
+          <t>16361; 37813</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>38034; 70596</t>
+          <t>37997; 69092</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>45265; 75703</t>
+          <t>42919; 73800</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>33540; 64393</t>
+          <t>36731; 68632</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>97735</t>
+          <t>109186</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>24487</t>
+          <t>31247</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>122222</t>
+          <t>140433</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>38924; 66093</t>
+          <t>39033; 67920</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>115514; 162242</t>
+          <t>114463; 163599</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>85564; 128607</t>
+          <t>86421; 127534</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>77979; 121734</t>
+          <t>87427; 134739</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>7108; 22856</t>
+          <t>7166; 22250</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13863; 34593</t>
+          <t>13739; 35819</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26546; 51518</t>
+          <t>27421; 51923</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>12493; 37468</t>
+          <t>21744; 45524</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>50788; 83364</t>
+          <t>49996; 81576</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>133873; 187440</t>
+          <t>135889; 185844</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>117227; 165883</t>
+          <t>120909; 168154</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>93197; 150627</t>
+          <t>118684; 169199</t>
         </is>
       </c>
     </row>
